--- a/data/trans_bre/IP19C08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 9,22</t>
+          <t>-5,03; 8,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 4,7</t>
+          <t>-6,22; 4,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 10,16</t>
+          <t>-4,53; 10,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,08; 9,54</t>
+          <t>0,11; 9,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,48; 295,5</t>
+          <t>-54,63; 259,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-85,12; 311,29</t>
+          <t>-87,33; 302,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,39; 498,77</t>
+          <t>-58,0; 409,75</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-64,91; —</t>
+          <t>-73,54; —</t>
         </is>
       </c>
     </row>
@@ -760,32 +760,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 5,75</t>
+          <t>-3,88; 5,8</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,77</t>
+          <t>-4,15; 3,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 5,08</t>
+          <t>-1,21; 5,21</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 3,6</t>
+          <t>-3,47; 3,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-53,43; 198,59</t>
+          <t>-52,55; 189,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,51; 260,87</t>
+          <t>-75,65; 240,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 315,33</t>
+          <t>-85,01; 389,35</t>
         </is>
       </c>
     </row>
@@ -860,27 +860,27 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 7,08</t>
+          <t>-4,08; 8,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 9,02</t>
+          <t>-0,86; 8,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 6,0</t>
+          <t>-2,94; 5,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,97; 0,61</t>
+          <t>-15,65; 0,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-71,86; 336,86</t>
+          <t>-61,35; 362,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-74,39; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,32 +960,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 4,77</t>
+          <t>-2,71; 4,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 5,65</t>
+          <t>-5,28; 5,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,93</t>
+          <t>-2,68; 3,03</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,61; -0,19</t>
+          <t>-7,57; 0,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,78; 225,78</t>
+          <t>-73,68; 215,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 223,49</t>
+          <t>-100,0; 283,29</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 3,63</t>
+          <t>-1,69; 3,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,2; 2,87</t>
+          <t>-1,85; 2,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 3,49</t>
+          <t>-0,93; 3,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,86</t>
+          <t>-4,22; 0,92</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-27,65; 112,01</t>
+          <t>-29,28; 108,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 104,03</t>
+          <t>-40,03; 101,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-29,56; 224,81</t>
+          <t>-26,32; 211,14</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-78,35; 48,89</t>
+          <t>-76,9; 55,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,03; 8,92</t>
+          <t>-5,64; 8,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 4,75</t>
+          <t>-5,59; 4,45</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 10,97</t>
+          <t>-3,97; 10,26</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 9,14</t>
+          <t>0,5; 10,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 259,14</t>
+          <t>-56,68; 224,98</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-87,33; 302,48</t>
+          <t>-85,36; 332,01</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-58,0; 409,75</t>
+          <t>-50,71; 444,95</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-73,54; —</t>
+          <t>-51,0; —</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 5,8</t>
+          <t>-3,92; 5,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 3,54</t>
+          <t>-3,63; 4,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 5,21</t>
+          <t>-1,27; 4,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 3,63</t>
+          <t>-3,6; 3,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-52,55; 189,14</t>
+          <t>-54,29; 188,15</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-75,65; 240,02</t>
+          <t>-74,86; 322,31</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-69,07; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-85,01; 389,35</t>
+          <t>-100,0; 348,99</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 8,04</t>
+          <t>-4,69; 7,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 8,74</t>
+          <t>-0,63; 9,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 5,86</t>
+          <t>-2,99; 6,03</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,65; 0,4</t>
+          <t>-15,41; 0,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,35; 362,42</t>
+          <t>-64,53; 286,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-89,96; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-74,39; —</t>
+          <t>-79,52; 901,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,22 +960,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 4,4</t>
+          <t>-2,92; 3,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 5,59</t>
+          <t>-5,31; 5,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 3,03</t>
+          <t>-2,7; 2,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 0,17</t>
+          <t>-7,59; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,68; 215,96</t>
+          <t>-72,17; 241,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 283,29</t>
+          <t>-100,0; 131,93</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 3,8</t>
+          <t>-1,93; 3,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 2,7</t>
+          <t>-1,98; 2,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 3,36</t>
+          <t>-1,13; 3,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,22; 0,92</t>
+          <t>-4,34; 0,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-29,28; 108,92</t>
+          <t>-32,14; 98,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-40,03; 101,22</t>
+          <t>-39,02; 110,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-26,32; 211,14</t>
+          <t>-31,49; 190,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-76,9; 55,14</t>
+          <t>-74,56; 49,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3,88</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>330,65%</t>
+          <t>401,87%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 8,76</t>
+          <t>-5,23; 9,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 4,45</t>
+          <t>-6,32; 4,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 10,26</t>
+          <t>-4,41; 10,16</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,5; 10,11</t>
+          <t>0,29; 9,25</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-56,68; 224,98</t>
+          <t>-58,48; 295,5</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-85,36; 332,01</t>
+          <t>-85,12; 311,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-50,71; 444,95</t>
+          <t>-55,39; 498,77</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,0; —</t>
+          <t>-66,89; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,05</t>
+          <t>0,01</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,93%</t>
+          <t>0,39%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 5,96</t>
+          <t>-3,75; 5,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 4,2</t>
+          <t>-4,17; 3,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 4,99</t>
+          <t>-1,29; 5,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 3,59</t>
+          <t>-3,74; 3,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,29; 188,15</t>
+          <t>-53,43; 198,59</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,86; 322,31</t>
+          <t>-75,51; 260,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-69,07; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 348,99</t>
+          <t>-100,0; 341,73</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,05</t>
+          <t>-4,42</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-78,01%</t>
+          <t>-80,76%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,69; 7,28</t>
+          <t>-5,04; 7,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 9,99</t>
+          <t>-0,64; 9,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 6,03</t>
+          <t>-3,1; 6,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 0,46</t>
+          <t>-18,53; 0,49</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,53; 286,91</t>
+          <t>-71,86; 336,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-89,96; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,52; 901,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-3,22</t>
+          <t>-3,19</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-78,6%</t>
+          <t>-77,69%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,92; 3,98</t>
+          <t>-2,85; 4,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 5,08</t>
+          <t>-5,34; 5,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,38</t>
+          <t>-2,7; 2,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 0,0</t>
+          <t>-7,63; -0,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>-100,0; —</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>-70,78; 225,78</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-72,17; 241,15</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 131,93</t>
+          <t>-100,0; 156,19</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-1,17</t>
+          <t>-1,19</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-34,5%</t>
+          <t>-35,39%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,47</t>
+          <t>-1,57; 3,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 2,68</t>
+          <t>-2,2; 2,87</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 3,23</t>
+          <t>-0,98; 3,49</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 0,9</t>
+          <t>-4,98; 0,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-32,14; 98,14</t>
+          <t>-27,65; 112,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-39,02; 110,87</t>
+          <t>-43,37; 104,03</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-31,49; 190,32</t>
+          <t>-29,56; 224,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-74,56; 49,21</t>
+          <t>-80,66; 46,59</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C08-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C08-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,193 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,43</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-0,8</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3,75</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20,53%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-17,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,52%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>401,87%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.425084230274462</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-0.7950396960812782</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.59688145990155</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>3.754841267018977</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.2052687024431087</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1756936107775771</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.4451888396947812</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>4.018678947909499</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-5,23; 9,22</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-6,32; 4,7</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-4,41; 10,16</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0,29; 9,25</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-58,48; 295,5</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-85,12; 311,29</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-55,39; 498,77</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-66,89; —</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-5.228470921245186</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-6.32322683141582</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-4.406373085358721</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.2935944355856837</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.584773974280441</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.8511815367922467</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.5539490396981872</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.6688928453746633</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>9.223087759363114</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.697655554466297</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>10.16388647966339</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9.250467018804677</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>2.955005022785879</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>3.11294038705336</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>4.987691947255322</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>1,03</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-0,05</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1,69</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19,44%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-1,36%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>101,91%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-3,75; 5,75</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,17; 3,77</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-1,29; 5,08</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,74; 3,65</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-53,43; 198,59</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-75,51; 260,87</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 341,73</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>1.034935449216569</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-0.04887142794670687</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.691843815975558</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.01048323966406882</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1944237629671544</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.01359472828796057</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>1.019080151091318</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.003944163512887035</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>1,14</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>3,16</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,45</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-4,42</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>22,66%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>200,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>52,88%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-80,76%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-3.746030149255587</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.172098325447144</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.286738512872657</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.743720046137895</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.5343039134414128</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7550804788350227</v>
+      </c>
+      <c r="I8" s="6" t="inlineStr"/>
+      <c r="J8" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-5,04; 7,08</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-0,64; 9,02</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-3,1; 6,0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-18,53; 0,49</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-71,86; 336,86</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.748304093773379</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>3.769422772689551</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>5.079610248836008</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>3.654922444070185</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.985940045800325</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>2.608743437840859</v>
+      </c>
+      <c r="I9" s="6" t="inlineStr"/>
+      <c r="J9" s="6" t="n">
+        <v>3.417324418773582</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +813,279 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>0,42</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,21</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,33</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,19</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>19,84%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-4,14%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-24,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-77,69%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>1.142973587101267</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>3.162777990614186</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.452860007576097</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-4.415308174835348</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.2265534504222621</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>2.000633424422796</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.5288390489809546</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.8076293808879951</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,85; 4,77</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-5,34; 5,65</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-2,7; 2,93</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-7,63; -0,08</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; —</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-70,78; 225,78</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 156,19</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.037990031310185</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-0.644997894517775</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-3.104148607851924</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-18.53252224974376</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.7185542969326587</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr"/>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>7.076847451936652</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>9.016617860494419</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>5.998750305199765</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.4918875993903857</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>3.368618719599765</v>
+      </c>
+      <c r="H12" s="6" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr"/>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>0.41784834425398</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.2149468079803332</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.3327319117122122</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-3.194620222833697</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>0.1983850402711801</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.04139020346313776</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.2490355076640107</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.7768578833109995</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.854118487494955</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-5.335695940884052</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-2.702712546325996</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-7.626073220971119</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.7077784537213979</v>
+      </c>
+      <c r="I14" s="6" t="inlineStr"/>
+      <c r="J14" s="6" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>4.7731731204893</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.64689047722211</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.934244806482192</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>-0.07675548510824774</v>
+      </c>
+      <c r="G15" s="6" t="inlineStr"/>
+      <c r="H15" s="6" t="n">
+        <v>2.257773427900426</v>
+      </c>
+      <c r="I15" s="6" t="inlineStr"/>
+      <c r="J15" s="6" t="n">
+        <v>1.561935293516777</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>0,88</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>0,44</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,17</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,19</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>18,19%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,81%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>44,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-35,39%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-1,57; 3,63</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-2,2; 2,87</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-0,98; 3,49</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,98; 0,83</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-27,65; 112,01</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-43,37; 104,03</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-29,56; 224,81</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-80,66; 46,59</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>0.8787124413446652</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.4448692499210684</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.169473112872999</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-1.192126196924952</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>0.1819113149722423</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.1180711723481298</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.4420876906362824</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.3539366863001872</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-1.574532706912602</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.204999073967761</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-0.97955425636728</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-4.983185191467434</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2764832455049856</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.4337334115989743</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.2956085855526211</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.8066301299534092</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>3.627750789319445</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.871438786975572</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.489782038389122</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.8330199795247242</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>1.120076726868758</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>1.040336738483317</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>2.248101233475155</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.465908947781777</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1093,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
